--- a/Stat Reviews/OT24_StatReview/scotusblog_replication/data/days_elapsed.xlsx
+++ b/Stat Reviews/OT24_StatReview/scotusblog_replication/data/days_elapsed.xlsx
@@ -61,21 +61,24 @@
     <t xml:space="preserve">Jackson</t>
   </si>
   <si>
+    <t xml:space="preserve">Advocate Christ Medical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barrett</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(7-2)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Vanderstok</t>
   </si>
   <si>
     <t xml:space="preserve">Gorsuch</t>
   </si>
   <si>
-    <t xml:space="preserve">(7-2)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Medical Marijuana</t>
   </si>
   <si>
-    <t xml:space="preserve">Barrett</t>
-  </si>
-  <si>
     <t xml:space="preserve">(5-4)</t>
   </si>
   <si>
@@ -85,19 +88,16 @@
     <t xml:space="preserve">(6-3)</t>
   </si>
   <si>
-    <t xml:space="preserve">Lackey</t>
+    <t xml:space="preserve">Feliciano</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mean_elapsed</t>
   </si>
   <si>
     <t xml:space="preserve">Roberts</t>
   </si>
   <si>
-    <t xml:space="preserve">Bufkin</t>
-  </si>
-  <si>
     <t xml:space="preserve">Thomas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mean_elapsed</t>
   </si>
   <si>
     <t xml:space="preserve">Sotomayor</t>
@@ -599,7 +599,7 @@
         <v>15</v>
       </c>
       <c r="B2" t="n">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="C2" t="s">
         <v>16</v>
@@ -608,10 +608,10 @@
         <v>17</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>45573</v>
+        <v>45601</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>45742</v>
+        <v>45776</v>
       </c>
     </row>
     <row r="3">
@@ -625,73 +625,73 @@
         <v>19</v>
       </c>
       <c r="D3" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>45580</v>
+        <v>45573</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>45749</v>
+        <v>45742</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B4" t="n">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="C4" t="s">
         <v>16</v>
       </c>
       <c r="D4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>45608</v>
+        <v>45580</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>45769</v>
+        <v>45749</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" t="n">
+        <v>162</v>
+      </c>
+      <c r="C5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" t="s">
         <v>23</v>
       </c>
-      <c r="B5" t="n">
-        <v>141</v>
-      </c>
-      <c r="C5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" t="s">
-        <v>17</v>
-      </c>
       <c r="E5" s="1" t="n">
-        <v>45573</v>
+        <v>45608</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>45713</v>
+        <v>45769</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B6" t="n">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C6" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D6" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>45581</v>
+        <v>45635</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>45721</v>
+        <v>45777</v>
       </c>
     </row>
   </sheetData>
@@ -710,12 +710,12 @@
         <v>2</v>
       </c>
       <c r="B1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B2" t="n">
         <v>104</v>
@@ -723,7 +723,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B3" t="n">
         <v>135.5</v>
@@ -755,10 +755,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B7" t="n">
-        <v>166</v>
+        <v>158.33</v>
       </c>
     </row>
     <row r="8">
@@ -771,10 +771,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>170</v>
+        <v>173</v>
       </c>
     </row>
     <row r="10">

--- a/Stat Reviews/OT24_StatReview/scotusblog_replication/data/days_elapsed.xlsx
+++ b/Stat Reviews/OT24_StatReview/scotusblog_replication/data/days_elapsed.xlsx
@@ -750,7 +750,7 @@
         <v>29</v>
       </c>
       <c r="B6" t="n">
-        <v>96.33</v>
+        <v>100.75</v>
       </c>
     </row>
     <row r="7">

--- a/Stat Reviews/OT24_StatReview/scotusblog_replication/data/days_elapsed.xlsx
+++ b/Stat Reviews/OT24_StatReview/scotusblog_replication/data/days_elapsed.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t xml:space="preserve">short_hand</t>
   </si>
@@ -46,6 +46,12 @@
     <t xml:space="preserve">Facebook</t>
   </si>
   <si>
+    <t xml:space="preserve">Drummond</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(4-4)*</t>
+  </si>
+  <si>
     <t xml:space="preserve">NVIDIA</t>
   </si>
   <si>
@@ -55,58 +61,55 @@
     <t xml:space="preserve">Alito</t>
   </si>
   <si>
-    <t xml:space="preserve">Bouarafa</t>
+    <t xml:space="preserve">Advocate Christ Medical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barrett</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(7-2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seven County</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kavanaugh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(8-0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vanderstok</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gorsuch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medical Marijuana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(5-4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kouisisis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mean_elapsed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roberts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thomas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sotomayor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kagan</t>
   </si>
   <si>
     <t xml:space="preserve">Jackson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Advocate Christ Medical</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Barrett</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(7-2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vanderstok</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gorsuch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medical Marijuana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(5-4)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Velazquez</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(6-3)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Feliciano</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mean_elapsed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roberts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thomas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sotomayor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kagan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kavanaugh</t>
   </si>
 </sst>
 </file>
@@ -508,39 +511,39 @@
         <v>10</v>
       </c>
       <c r="B4" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C4" t="s">
         <v>7</v>
       </c>
       <c r="D4" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>45609</v>
+        <v>45777</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>45637</v>
+        <v>45799</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>45671</v>
+        <v>45609</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>45714</v>
+        <v>45637</v>
       </c>
     </row>
     <row r="6">
@@ -548,7 +551,7 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="C6" t="s">
         <v>14</v>
@@ -557,10 +560,10 @@
         <v>8</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>45580</v>
+        <v>45671</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>45636</v>
+        <v>45714</v>
       </c>
     </row>
   </sheetData>
@@ -619,79 +622,79 @@
         <v>18</v>
       </c>
       <c r="B3" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C3" t="s">
         <v>19</v>
       </c>
       <c r="D3" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>45573</v>
+        <v>45636</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>45742</v>
+        <v>45806</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B4" t="n">
         <v>170</v>
       </c>
       <c r="C4" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="D4" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>45580</v>
+        <v>45573</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>45749</v>
+        <v>45742</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B5" t="n">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>45608</v>
+        <v>45580</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>45769</v>
+        <v>45749</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B6" t="n">
-        <v>143</v>
+        <v>165</v>
       </c>
       <c r="C6" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D6" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="E6" s="1" t="n">
         <v>45635</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>45777</v>
+        <v>45799</v>
       </c>
     </row>
   </sheetData>
@@ -710,12 +713,12 @@
         <v>2</v>
       </c>
       <c r="B1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B2" t="n">
         <v>104</v>
@@ -723,7 +726,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B3" t="n">
         <v>135.5</v>
@@ -731,7 +734,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B4" t="n">
         <v>102</v>
@@ -739,7 +742,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B5" t="n">
         <v>102.33</v>
@@ -747,7 +750,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B6" t="n">
         <v>100.75</v>
@@ -755,7 +758,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B7" t="n">
         <v>158.33</v>
@@ -763,10 +766,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>127</v>
       </c>
     </row>
     <row r="9">
@@ -774,12 +777,12 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>173</v>
+        <v>170.33</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="B10" t="n">
         <v>86</v>

--- a/Stat Reviews/OT24_StatReview/scotusblog_replication/data/days_elapsed.xlsx
+++ b/Stat Reviews/OT24_StatReview/scotusblog_replication/data/days_elapsed.xlsx
@@ -55,52 +55,52 @@
     <t xml:space="preserve">NVIDIA</t>
   </si>
   <si>
-    <t xml:space="preserve">Waetzig</t>
+    <t xml:space="preserve">Laboratory Corp.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Advocate Christ Medical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barrett</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(7-2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seven County</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kavanaugh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(8-0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vanderstok</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gorsuch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medical Marijuana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(5-4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kouisisis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mean_elapsed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roberts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thomas</t>
   </si>
   <si>
     <t xml:space="preserve">Alito</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Advocate Christ Medical</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Barrett</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(7-2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seven County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kavanaugh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(8-0)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vanderstok</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gorsuch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medical Marijuana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(5-4)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kouisisis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mean_elapsed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roberts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thomas</t>
   </si>
   <si>
     <t xml:space="preserve">Sotomayor</t>
@@ -551,19 +551,19 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="C6" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D6" t="s">
         <v>8</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>45671</v>
+        <v>45776</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>45714</v>
+        <v>45813</v>
       </c>
     </row>
   </sheetData>
@@ -599,16 +599,16 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B2" t="n">
         <v>176</v>
       </c>
       <c r="C2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" t="s">
         <v>16</v>
-      </c>
-      <c r="D2" t="s">
-        <v>17</v>
       </c>
       <c r="E2" s="1" t="n">
         <v>45601</v>
@@ -619,16 +619,16 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B3" t="n">
         <v>171</v>
       </c>
       <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
         <v>19</v>
-      </c>
-      <c r="D3" t="s">
-        <v>20</v>
       </c>
       <c r="E3" s="1" t="n">
         <v>45636</v>
@@ -639,16 +639,16 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B4" t="n">
         <v>170</v>
       </c>
       <c r="C4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E4" s="1" t="n">
         <v>45573</v>
@@ -659,16 +659,16 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B5" t="n">
         <v>170</v>
       </c>
       <c r="C5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E5" s="1" t="n">
         <v>45580</v>
@@ -679,13 +679,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B6" t="n">
         <v>165</v>
       </c>
       <c r="C6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D6" t="s">
         <v>8</v>
@@ -713,12 +713,12 @@
         <v>2</v>
       </c>
       <c r="B1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B2" t="n">
         <v>104</v>
@@ -726,18 +726,18 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B3" t="n">
-        <v>135.5</v>
+        <v>122</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B4" t="n">
-        <v>102</v>
+        <v>100.25</v>
       </c>
     </row>
     <row r="5">
@@ -745,7 +745,7 @@
         <v>29</v>
       </c>
       <c r="B5" t="n">
-        <v>102.33</v>
+        <v>93.5</v>
       </c>
     </row>
     <row r="6">
@@ -753,12 +753,12 @@
         <v>30</v>
       </c>
       <c r="B6" t="n">
-        <v>100.75</v>
+        <v>99.4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B7" t="n">
         <v>158.33</v>
@@ -766,7 +766,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B8" t="n">
         <v>127</v>
@@ -774,7 +774,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B9" t="n">
         <v>170.33</v>
@@ -785,7 +785,7 @@
         <v>31</v>
       </c>
       <c r="B10" t="n">
-        <v>86</v>
+        <v>90.67</v>
       </c>
     </row>
   </sheetData>

--- a/Stat Reviews/OT24_StatReview/scotusblog_replication/data/days_elapsed.xlsx
+++ b/Stat Reviews/OT24_StatReview/scotusblog_replication/data/days_elapsed.xlsx
@@ -721,7 +721,7 @@
         <v>26</v>
       </c>
       <c r="B2" t="n">
-        <v>104</v>
+        <v>84.67</v>
       </c>
     </row>
     <row r="3">
@@ -729,7 +729,7 @@
         <v>27</v>
       </c>
       <c r="B3" t="n">
-        <v>122</v>
+        <v>103</v>
       </c>
     </row>
     <row r="4">
@@ -745,7 +745,7 @@
         <v>29</v>
       </c>
       <c r="B5" t="n">
-        <v>93.5</v>
+        <v>85.4</v>
       </c>
     </row>
     <row r="6">
@@ -761,7 +761,7 @@
         <v>21</v>
       </c>
       <c r="B7" t="n">
-        <v>158.33</v>
+        <v>130</v>
       </c>
     </row>
     <row r="8">
@@ -777,7 +777,7 @@
         <v>15</v>
       </c>
       <c r="B9" t="n">
-        <v>170.33</v>
+        <v>140.75</v>
       </c>
     </row>
     <row r="10">
@@ -785,7 +785,7 @@
         <v>31</v>
       </c>
       <c r="B10" t="n">
-        <v>90.67</v>
+        <v>86.5</v>
       </c>
     </row>
   </sheetData>

--- a/Stat Reviews/OT24_StatReview/scotusblog_replication/data/days_elapsed.xlsx
+++ b/Stat Reviews/OT24_StatReview/scotusblog_replication/data/days_elapsed.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t xml:space="preserve">short_hand</t>
   </si>
@@ -58,6 +58,15 @@
     <t xml:space="preserve">Laboratory Corp.</t>
   </si>
   <si>
+    <t xml:space="preserve">Skrmetti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roberts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(6-3)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Advocate Christ Medical</t>
   </si>
   <si>
@@ -88,13 +97,7 @@
     <t xml:space="preserve">(5-4)</t>
   </si>
   <si>
-    <t xml:space="preserve">Kouisisis</t>
-  </si>
-  <si>
     <t xml:space="preserve">mean_elapsed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roberts</t>
   </si>
   <si>
     <t xml:space="preserve">Thomas</t>
@@ -602,7 +605,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="n">
-        <v>176</v>
+        <v>197</v>
       </c>
       <c r="C2" t="s">
         <v>15</v>
@@ -611,10 +614,10 @@
         <v>16</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>45601</v>
+        <v>45630</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>45776</v>
+        <v>45826</v>
       </c>
     </row>
     <row r="3">
@@ -622,7 +625,7 @@
         <v>17</v>
       </c>
       <c r="B3" t="n">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="C3" t="s">
         <v>18</v>
@@ -631,10 +634,10 @@
         <v>19</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>45636</v>
+        <v>45601</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>45806</v>
+        <v>45776</v>
       </c>
     </row>
     <row r="4">
@@ -642,59 +645,59 @@
         <v>20</v>
       </c>
       <c r="B4" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C4" t="s">
         <v>21</v>
       </c>
       <c r="D4" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>45573</v>
+        <v>45636</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>45742</v>
+        <v>45806</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B5" t="n">
         <v>170</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="D5" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>45580</v>
+        <v>45573</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>45749</v>
+        <v>45742</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B6" t="n">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="C6" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D6" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>45635</v>
+        <v>45580</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>45799</v>
+        <v>45749</v>
       </c>
     </row>
   </sheetData>
@@ -713,28 +716,28 @@
         <v>2</v>
       </c>
       <c r="B1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="B2" t="n">
-        <v>84.67</v>
+        <v>107.67</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B3" t="n">
-        <v>103</v>
+        <v>97.33</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B4" t="n">
         <v>100.25</v>
@@ -742,7 +745,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B5" t="n">
         <v>85.4</v>
@@ -750,7 +753,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B6" t="n">
         <v>99.4</v>
@@ -758,31 +761,31 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B7" t="n">
-        <v>130</v>
+        <v>135.8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B8" t="n">
-        <v>127</v>
+        <v>116.17</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B9" t="n">
-        <v>140.75</v>
+        <v>138.33</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B10" t="n">
         <v>86.5</v>

--- a/Stat Reviews/OT24_StatReview/scotusblog_replication/data/days_elapsed.xlsx
+++ b/Stat Reviews/OT24_StatReview/scotusblog_replication/data/days_elapsed.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t xml:space="preserve">short_hand</t>
   </si>
@@ -56,6 +56,9 @@
   </si>
   <si>
     <t xml:space="preserve">Laboratory Corp.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(8-1)</t>
   </si>
   <si>
     <t xml:space="preserve">Skrmetti</t>
@@ -560,7 +563,7 @@
         <v>7</v>
       </c>
       <c r="D6" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E6" s="1" t="n">
         <v>45776</v>
@@ -602,16 +605,16 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2" t="n">
         <v>197</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E2" s="1" t="n">
         <v>45630</v>
@@ -622,16 +625,16 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B3" t="n">
         <v>176</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E3" s="1" t="n">
         <v>45601</v>
@@ -642,16 +645,16 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B4" t="n">
         <v>171</v>
       </c>
       <c r="C4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E4" s="1" t="n">
         <v>45636</v>
@@ -662,16 +665,16 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B5" t="n">
         <v>170</v>
       </c>
       <c r="C5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E5" s="1" t="n">
         <v>45573</v>
@@ -682,16 +685,16 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B6" t="n">
         <v>170</v>
       </c>
       <c r="C6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E6" s="1" t="n">
         <v>45580</v>
@@ -716,12 +719,12 @@
         <v>2</v>
       </c>
       <c r="B1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B2" t="n">
         <v>107.67</v>
@@ -729,7 +732,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B3" t="n">
         <v>97.33</v>
@@ -737,7 +740,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B4" t="n">
         <v>100.25</v>
@@ -745,7 +748,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B5" t="n">
         <v>85.4</v>
@@ -753,7 +756,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B6" t="n">
         <v>99.4</v>
@@ -761,7 +764,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B7" t="n">
         <v>135.8</v>
@@ -769,7 +772,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B8" t="n">
         <v>116.17</v>
@@ -777,7 +780,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B9" t="n">
         <v>138.33</v>
@@ -785,7 +788,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B10" t="n">
         <v>86.5</v>

--- a/Stat Reviews/OT24_StatReview/scotusblog_replication/data/days_elapsed.xlsx
+++ b/Stat Reviews/OT24_StatReview/scotusblog_replication/data/days_elapsed.xlsx
@@ -743,7 +743,7 @@
         <v>30</v>
       </c>
       <c r="B4" t="n">
-        <v>100.25</v>
+        <v>99.2</v>
       </c>
     </row>
     <row r="5">
@@ -751,7 +751,7 @@
         <v>31</v>
       </c>
       <c r="B5" t="n">
-        <v>85.4</v>
+        <v>91.67</v>
       </c>
     </row>
     <row r="6">
@@ -767,7 +767,7 @@
         <v>25</v>
       </c>
       <c r="B7" t="n">
-        <v>135.8</v>
+        <v>127.5</v>
       </c>
     </row>
     <row r="8">
@@ -791,7 +791,7 @@
         <v>33</v>
       </c>
       <c r="B10" t="n">
-        <v>86.5</v>
+        <v>102.2</v>
       </c>
     </row>
   </sheetData>

--- a/Stat Reviews/OT24_StatReview/scotusblog_replication/data/days_elapsed.xlsx
+++ b/Stat Reviews/OT24_StatReview/scotusblog_replication/data/days_elapsed.xlsx
@@ -735,7 +735,7 @@
         <v>29</v>
       </c>
       <c r="B3" t="n">
-        <v>97.33</v>
+        <v>106.86</v>
       </c>
     </row>
     <row r="4">
@@ -743,7 +743,7 @@
         <v>30</v>
       </c>
       <c r="B4" t="n">
-        <v>99.2</v>
+        <v>93.83</v>
       </c>
     </row>
     <row r="5">
@@ -759,7 +759,7 @@
         <v>32</v>
       </c>
       <c r="B6" t="n">
-        <v>99.4</v>
+        <v>98.5</v>
       </c>
     </row>
     <row r="7">
@@ -775,7 +775,7 @@
         <v>22</v>
       </c>
       <c r="B8" t="n">
-        <v>116.17</v>
+        <v>109.29</v>
       </c>
     </row>
     <row r="9">
@@ -783,7 +783,7 @@
         <v>19</v>
       </c>
       <c r="B9" t="n">
-        <v>138.33</v>
+        <v>124.86</v>
       </c>
     </row>
     <row r="10">
